--- a/projects/Barana_2009/cases_summary.xlsx
+++ b/projects/Barana_2009/cases_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="13">
   <si>
     <t>Case</t>
   </si>
@@ -49,6 +49,9 @@
     <t>equilibrium</t>
   </si>
   <si>
+    <t>blending</t>
+  </si>
+  <si>
     <t xml:space="preserve">equilibrium
 </t>
   </si>
@@ -61,7 +64,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="#,##0.0000"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -79,12 +82,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -131,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -154,22 +151,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="165" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -180,6 +171,9 @@
     </xf>
     <xf xfId="0" numFmtId="1" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="164" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -492,15 +486,15 @@
   <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="18" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="16" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="17" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -552,7 +546,7 @@
         <v>10</v>
       </c>
       <c r="G2" s="10">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H2" s="10">
         <v>0.05</v>
@@ -581,7 +575,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="10">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H3" s="10">
         <v>0.05</v>
@@ -610,7 +604,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="10">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H4" s="10">
         <v>0.05</v>
@@ -620,7 +614,7 @@
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
-      <c r="A5" s="12">
+      <c r="A5" s="6">
         <v>4</v>
       </c>
       <c r="B5" s="7" t="s">
@@ -629,7 +623,7 @@
       <c r="C5" s="6">
         <v>9000000</v>
       </c>
-      <c r="D5" s="12">
+      <c r="D5" s="6">
         <v>40</v>
       </c>
       <c r="E5" s="8">
@@ -639,17 +633,17 @@
         <v>10</v>
       </c>
       <c r="G5" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H5" s="10">
         <v>0.05</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="11">
         <v>0.0182</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
-      <c r="A6" s="12">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
       <c r="B6" s="7" t="s">
@@ -658,7 +652,7 @@
       <c r="C6" s="6">
         <v>9000000</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="6">
         <v>40</v>
       </c>
       <c r="E6" s="8">
@@ -668,17 +662,17 @@
         <v>10</v>
       </c>
       <c r="G6" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H6" s="10">
         <v>0.05</v>
       </c>
-      <c r="I6" s="13">
+      <c r="I6" s="11">
         <v>0.019</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
-      <c r="A7" s="12">
+      <c r="A7" s="6">
         <v>6</v>
       </c>
       <c r="B7" s="7" t="s">
@@ -687,7 +681,7 @@
       <c r="C7" s="6">
         <v>9000000</v>
       </c>
-      <c r="D7" s="12">
+      <c r="D7" s="6">
         <v>40</v>
       </c>
       <c r="E7" s="8">
@@ -697,17 +691,17 @@
         <v>10</v>
       </c>
       <c r="G7" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H7" s="10">
         <v>0.05</v>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="11">
         <v>0.0204</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
-      <c r="A8" s="12">
+      <c r="A8" s="6">
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -716,7 +710,7 @@
       <c r="C8" s="6">
         <v>9000000</v>
       </c>
-      <c r="D8" s="12">
+      <c r="D8" s="6">
         <v>40</v>
       </c>
       <c r="E8" s="8">
@@ -726,17 +720,17 @@
         <v>10</v>
       </c>
       <c r="G8" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H8" s="10">
         <v>0.05</v>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="11">
         <v>0.019</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
-      <c r="A9" s="12">
+      <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="7" t="s">
@@ -745,7 +739,7 @@
       <c r="C9" s="6">
         <v>9000000</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="6">
         <v>40</v>
       </c>
       <c r="E9" s="8">
@@ -755,12 +749,12 @@
         <v>10</v>
       </c>
       <c r="G9" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H9" s="10">
         <v>0.05</v>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="11">
         <v>0.02</v>
       </c>
     </row>
@@ -774,22 +768,22 @@
       <c r="C10" s="6">
         <v>9000000</v>
       </c>
-      <c r="D10" s="12">
+      <c r="D10" s="6">
         <v>45</v>
       </c>
       <c r="E10" s="8">
         <v>3550000</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H10" s="10">
         <v>0.05</v>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="11">
         <v>0.0172</v>
       </c>
     </row>
@@ -803,22 +797,22 @@
       <c r="C11" s="6">
         <v>9000000</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="6">
         <v>45</v>
       </c>
       <c r="E11" s="8">
         <v>3880000</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H11" s="10">
         <v>0.05</v>
       </c>
-      <c r="I11" s="13">
+      <c r="I11" s="11">
         <v>0.019</v>
       </c>
     </row>
@@ -832,27 +826,27 @@
       <c r="C12" s="6">
         <v>9000000</v>
       </c>
-      <c r="D12" s="12">
+      <c r="D12" s="6">
         <v>45</v>
       </c>
       <c r="E12" s="8">
         <v>4120000</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H12" s="10">
         <v>0.05</v>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="11">
         <v>0.0185</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
-      <c r="A13" s="12">
+      <c r="A13" s="6">
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -861,27 +855,27 @@
       <c r="C13" s="6">
         <v>9000000</v>
       </c>
-      <c r="D13" s="12">
+      <c r="D13" s="6">
         <v>45</v>
       </c>
       <c r="E13" s="8">
         <v>5010000</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H13" s="10">
         <v>0.05</v>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="11">
         <v>0.0188</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
-      <c r="A14" s="12">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
@@ -890,65 +884,65 @@
       <c r="C14" s="6">
         <v>9000000</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="6">
         <v>45</v>
       </c>
       <c r="E14" s="8">
         <v>5690000</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="10">
-        <v>0.05</v>
+        <v>9</v>
       </c>
       <c r="H14" s="10">
         <v>0.05</v>
       </c>
-      <c r="I14" s="13">
+      <c r="I14" s="11">
         <v>0.0188</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
-      <c r="A15" s="12">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
+      <c r="A15" s="6">
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="6">
         <v>9000000</v>
       </c>
-      <c r="D15" s="12">
+      <c r="D15" s="6">
         <v>45</v>
       </c>
       <c r="E15" s="8">
         <v>5960000</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H15" s="10">
         <v>0.05</v>
       </c>
-      <c r="I15" s="13">
+      <c r="I15" s="11">
         <v>0.0188</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
-      <c r="A16" s="12">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
+      <c r="A16" s="6">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="6">
         <v>9500000</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="6">
         <v>40</v>
       </c>
       <c r="E16" s="8">
@@ -958,26 +952,26 @@
         <v>10</v>
       </c>
       <c r="G16" s="10">
-        <v>0.99</v>
+        <v>0.05</v>
       </c>
       <c r="H16" s="10">
         <v>0.05</v>
       </c>
-      <c r="I16" s="13">
+      <c r="I16" s="11">
         <v>0.0219</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
-      <c r="A17" s="12">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
+      <c r="A17" s="6">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="6">
         <v>9500000</v>
       </c>
-      <c r="D17" s="12">
+      <c r="D17" s="6">
         <v>40</v>
       </c>
       <c r="E17" s="8">
@@ -987,26 +981,26 @@
         <v>10</v>
       </c>
       <c r="G17" s="10">
-        <v>0.99</v>
+        <v>0.05</v>
       </c>
       <c r="H17" s="10">
         <v>0.05</v>
       </c>
-      <c r="I17" s="13">
+      <c r="I17" s="11">
         <v>0.0248</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
-      <c r="A18" s="12">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
+      <c r="A18" s="6">
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="6">
         <v>9500000</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="6">
         <v>40</v>
       </c>
       <c r="E18" s="8">
@@ -1016,403 +1010,403 @@
         <v>10</v>
       </c>
       <c r="G18" s="10">
-        <v>0.99</v>
+        <v>0.05</v>
       </c>
       <c r="H18" s="10">
         <v>0.05</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="11">
         <v>0.0249</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
-      <c r="A19" s="12">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
+      <c r="A19" s="6">
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="6">
         <v>9500000</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="6">
         <v>45</v>
       </c>
       <c r="E19" s="8">
         <v>3970000</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H19" s="10">
         <v>0.05</v>
       </c>
-      <c r="I19" s="13">
+      <c r="I19" s="11">
         <v>0.0188</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
-      <c r="A20" s="12">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
+      <c r="A20" s="6">
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="6">
         <v>9500000</v>
       </c>
-      <c r="D20" s="12">
+      <c r="D20" s="6">
         <v>45</v>
       </c>
       <c r="E20" s="8">
         <v>4290000</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H20" s="10">
         <v>0.05</v>
       </c>
-      <c r="I20" s="13">
+      <c r="I20" s="11">
         <v>0.0194</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
-      <c r="A21" s="12">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
+      <c r="A21" s="6">
         <v>20</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="6">
         <v>9500000</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="6">
         <v>45</v>
       </c>
       <c r="E21" s="8">
         <v>4630000</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H21" s="10">
         <v>0.05</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
-      <c r="A22" s="12">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
+      <c r="A22" s="6">
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="6">
         <v>9500000</v>
       </c>
-      <c r="D22" s="12">
+      <c r="D22" s="6">
         <v>45</v>
       </c>
       <c r="E22" s="8">
         <v>4860000</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H22" s="10">
         <v>0.05</v>
       </c>
-      <c r="I22" s="13">
+      <c r="I22" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
-      <c r="A23" s="12">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
+      <c r="A23" s="6">
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="6">
         <v>9500000</v>
       </c>
-      <c r="D23" s="12">
+      <c r="D23" s="6">
         <v>45</v>
       </c>
       <c r="E23" s="8">
         <v>5480000</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H23" s="10">
         <v>0.05</v>
       </c>
-      <c r="I23" s="13">
+      <c r="I23" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
-      <c r="A24" s="12">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
+      <c r="A24" s="6">
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="6">
         <v>9500000</v>
       </c>
-      <c r="D24" s="12">
+      <c r="D24" s="6">
         <v>45</v>
       </c>
       <c r="E24" s="8">
         <v>5810000</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" s="10">
-        <v>0.05</v>
+        <v>0.9</v>
       </c>
       <c r="H24" s="10">
         <v>0.05</v>
       </c>
-      <c r="I24" s="13">
+      <c r="I24" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
-      <c r="A25" s="12">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
+      <c r="A25" s="6">
         <v>24</v>
       </c>
       <c r="B25" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="6">
         <v>9500000</v>
       </c>
-      <c r="D25" s="12">
+      <c r="D25" s="6">
         <v>50</v>
       </c>
       <c r="E25" s="8">
         <v>3550000</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H25" s="10">
         <v>0.05</v>
       </c>
-      <c r="I25" s="13">
+      <c r="I25" s="11">
         <v>0.0193</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
-      <c r="A26" s="12">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
+      <c r="A26" s="6">
         <v>25</v>
       </c>
       <c r="B26" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="6">
         <v>9500000</v>
       </c>
-      <c r="D26" s="12">
+      <c r="D26" s="6">
         <v>50</v>
       </c>
       <c r="E26" s="8">
         <v>3850000</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H26" s="10">
         <v>0.05</v>
       </c>
-      <c r="I26" s="13">
+      <c r="I26" s="11">
         <v>0.0193</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
-      <c r="A27" s="12">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
+      <c r="A27" s="6">
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="6">
         <v>9500000</v>
       </c>
-      <c r="D27" s="12">
+      <c r="D27" s="6">
         <v>50</v>
       </c>
       <c r="E27" s="8">
         <v>4280000</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H27" s="10">
         <v>0.05</v>
       </c>
-      <c r="I27" s="13">
+      <c r="I27" s="11">
         <v>0.0187</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
-      <c r="A28" s="12">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
+      <c r="A28" s="6">
         <v>27</v>
       </c>
       <c r="B28" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="6">
         <v>9500000</v>
       </c>
-      <c r="D28" s="12">
+      <c r="D28" s="6">
         <v>50</v>
       </c>
       <c r="E28" s="8">
         <v>4600000</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H28" s="10">
         <v>0.05</v>
       </c>
-      <c r="I28" s="13">
+      <c r="I28" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
-      <c r="A29" s="12">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
+      <c r="A29" s="6">
         <v>28</v>
       </c>
       <c r="B29" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="6">
         <v>9500000</v>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="6">
         <v>50</v>
       </c>
       <c r="E29" s="8">
         <v>4990000</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H29" s="10">
         <v>0.05</v>
       </c>
-      <c r="I29" s="13">
+      <c r="I29" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
-      <c r="A30" s="12">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
+      <c r="A30" s="6">
         <v>29</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="6">
         <v>9500000</v>
       </c>
-      <c r="D30" s="12">
+      <c r="D30" s="6">
         <v>50</v>
       </c>
       <c r="E30" s="8">
         <v>5490000</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H30" s="10">
         <v>0.05</v>
       </c>
-      <c r="I30" s="13">
+      <c r="I30" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
-      <c r="A31" s="12">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
+      <c r="A31" s="6">
         <v>30</v>
       </c>
       <c r="B31" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="6">
         <v>9500000</v>
       </c>
-      <c r="D31" s="12">
+      <c r="D31" s="6">
         <v>50</v>
       </c>
       <c r="E31" s="8">
         <v>5850000</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H31" s="10">
         <v>0.05</v>
       </c>
-      <c r="I31" s="13">
+      <c r="I31" s="11">
         <v>0.0191</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
-      <c r="A32" s="12">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
+      <c r="A32" s="6">
         <v>31</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="6">
         <v>10000000</v>
       </c>
-      <c r="D32" s="12">
+      <c r="D32" s="6">
         <v>43</v>
       </c>
       <c r="E32" s="8">
@@ -1422,26 +1416,26 @@
         <v>10</v>
       </c>
       <c r="G32" s="10">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H32" s="10">
         <v>0.05</v>
       </c>
-      <c r="I32" s="13">
+      <c r="I32" s="11">
         <v>0.0233</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="12">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
+      <c r="A33" s="6">
         <v>32</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="6">
         <v>10000000</v>
       </c>
-      <c r="D33" s="12">
+      <c r="D33" s="6">
         <v>43</v>
       </c>
       <c r="E33" s="8">
@@ -1451,26 +1445,26 @@
         <v>10</v>
       </c>
       <c r="G33" s="10">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H33" s="10">
         <v>0.05</v>
       </c>
-      <c r="I33" s="13">
+      <c r="I33" s="11">
         <v>0.0242</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="12">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
+      <c r="A34" s="6">
         <v>33</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="6">
         <v>10000000</v>
       </c>
-      <c r="D34" s="12">
+      <c r="D34" s="6">
         <v>43</v>
       </c>
       <c r="E34" s="8">
@@ -1480,26 +1474,26 @@
         <v>10</v>
       </c>
       <c r="G34" s="10">
-        <v>0.95</v>
+        <v>0.05</v>
       </c>
       <c r="H34" s="10">
         <v>0.05</v>
       </c>
-      <c r="I34" s="13">
+      <c r="I34" s="11">
         <v>0.0255</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="12">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
+      <c r="A35" s="6">
         <v>34</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="6">
         <v>10000000</v>
       </c>
-      <c r="D35" s="12">
+      <c r="D35" s="6">
         <v>45</v>
       </c>
       <c r="E35" s="8">
@@ -1509,26 +1503,26 @@
         <v>10</v>
       </c>
       <c r="G35" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H35" s="10">
         <v>0.05</v>
       </c>
-      <c r="I35" s="13">
+      <c r="I35" s="11">
         <v>0.0247</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="12">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
+      <c r="A36" s="6">
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="6">
         <v>10000000</v>
       </c>
-      <c r="D36" s="12">
+      <c r="D36" s="6">
         <v>45</v>
       </c>
       <c r="E36" s="8">
@@ -1538,55 +1532,55 @@
         <v>10</v>
       </c>
       <c r="G36" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H36" s="10">
         <v>0.05</v>
       </c>
-      <c r="I36" s="13">
+      <c r="I36" s="11">
         <v>0.0242</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="12">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
+      <c r="A37" s="6">
         <v>36</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="6">
         <v>10000000</v>
       </c>
-      <c r="D37" s="12">
+      <c r="D37" s="6">
         <v>45</v>
       </c>
       <c r="E37" s="8">
         <v>5320000</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G37" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H37" s="10">
         <v>0.05</v>
       </c>
-      <c r="I37" s="13">
+      <c r="I37" s="11">
         <v>0.0242</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="12">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
+      <c r="A38" s="6">
         <v>37</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="6">
         <v>10000000</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D38" s="6">
         <v>45</v>
       </c>
       <c r="E38" s="8">
@@ -1596,186 +1590,186 @@
         <v>10</v>
       </c>
       <c r="G38" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H38" s="10">
         <v>0.05</v>
       </c>
-      <c r="I38" s="13">
+      <c r="I38" s="11">
         <v>0.0246</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="12">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
+      <c r="A39" s="6">
         <v>38</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="6">
         <v>10000000</v>
       </c>
-      <c r="D39" s="12">
+      <c r="D39" s="6">
         <v>50</v>
       </c>
       <c r="E39" s="8">
         <v>4200000</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H39" s="10">
         <v>0.05</v>
       </c>
-      <c r="I39" s="13">
+      <c r="I39" s="11">
         <v>0.02</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="12">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
+      <c r="A40" s="6">
         <v>39</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="6">
         <v>10000000</v>
       </c>
-      <c r="D40" s="12">
+      <c r="D40" s="6">
         <v>50</v>
       </c>
       <c r="E40" s="8">
         <v>4560000</v>
       </c>
       <c r="F40" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H40" s="10">
         <v>0.05</v>
       </c>
-      <c r="I40" s="13">
+      <c r="I40" s="11">
         <v>0.0215</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="12">
+      <c r="A41" s="6">
         <v>40</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="6">
         <v>10000000</v>
       </c>
-      <c r="D41" s="12">
+      <c r="D41" s="6">
         <v>50</v>
       </c>
       <c r="E41" s="8">
         <v>4860000</v>
       </c>
       <c r="F41" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H41" s="10">
         <v>0.05</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="11">
         <v>0.02</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="12">
+      <c r="A42" s="6">
         <v>41</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="6">
         <v>10000000</v>
       </c>
-      <c r="D42" s="12">
+      <c r="D42" s="6">
         <v>50</v>
       </c>
       <c r="E42" s="8">
         <v>5110000</v>
       </c>
       <c r="F42" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H42" s="10">
         <v>0.05</v>
       </c>
-      <c r="I42" s="13">
+      <c r="I42" s="11">
         <v>0.02</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="12">
+      <c r="A43" s="6">
         <v>42</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="6">
         <v>10000000</v>
       </c>
-      <c r="D43" s="12">
+      <c r="D43" s="6">
         <v>50</v>
       </c>
       <c r="E43" s="8">
         <v>5630000</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G43" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H43" s="10">
         <v>0.05</v>
       </c>
-      <c r="I43" s="13">
+      <c r="I43" s="11">
         <v>0.02</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="12">
+      <c r="A44" s="6">
         <v>43</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="6">
         <v>10000000</v>
       </c>
-      <c r="D44" s="12">
+      <c r="D44" s="6">
         <v>50</v>
       </c>
       <c r="E44" s="8">
         <v>5940000</v>
       </c>
       <c r="F44" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44" s="10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="H44" s="10">
         <v>0.05</v>
       </c>
-      <c r="I44" s="13">
+      <c r="I44" s="11">
         <v>0.02</v>
       </c>
     </row>
